--- a/Laboratorio2/mediciones/clase2/raw/mediciones_raw.xlsx
+++ b/Laboratorio2/mediciones/clase2/raw/mediciones_raw.xlsx
@@ -5,22 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kevin\Documents\UBA\Jacky\Laboratorio2\mediciones\clase2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kevin\Documents\UBA\Jacky\Laboratorio2\mediciones\clase2\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CDA050-FF2F-4E04-8B6F-FFDED09828F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941324A6-FF08-4941-8CA6-51A9E004FAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja 2" sheetId="2" r:id="rId2"/>
     <sheet name="Hoja 3" sheetId="3" r:id="rId3"/>
     <sheet name="Hoja 4" sheetId="4" r:id="rId4"/>
-    <sheet name="Hoja 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Hoja1" sheetId="6" r:id="rId5"/>
+    <sheet name="Hoja 5" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Frecuencia (Khz)</t>
   </si>
@@ -61,13 +73,7 @@
     <t>12.5M</t>
   </si>
   <si>
-    <t>delta T (microSeg)</t>
-  </si>
-  <si>
     <t>2DC-200mV</t>
-  </si>
-  <si>
-    <t>Vpp-Receptor</t>
   </si>
   <si>
     <t>2DC-20mV</t>
@@ -77,9 +83,6 @@
   </si>
   <si>
     <t>50mV</t>
-  </si>
-  <si>
-    <t>mas un periodo</t>
   </si>
   <si>
     <t>Vpp</t>
@@ -111,11 +114,32 @@
   <si>
     <t>Escala-receptor (mV)</t>
   </si>
+  <si>
+    <t>periodo (mS)</t>
+  </si>
+  <si>
+    <t>delta t (microSeg)</t>
+  </si>
+  <si>
+    <t>periodo (microS)</t>
+  </si>
+  <si>
+    <t>delta_total</t>
+  </si>
+  <si>
+    <t>2pi*delta_total</t>
+  </si>
+  <si>
+    <t>fase(rad)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -150,9 +174,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,7 +1040,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="es-AR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1090,7 +1115,7 @@
                     <a:latin typeface="+mn-lt"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr/>
+                <a:endParaRPr lang="es-AR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1154,6 +1179,975 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-AR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Hoja 4'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>fase(rad)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Hoja 4'!$A$2:$A$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>36.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>38.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>42.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Hoja 4'!$G$2:$G$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0">
+                  <c:v>0.86909019168908042</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5637591592508555</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2659679491812459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9757165614802519</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.6462580974624577</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.3238368009887038</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.0084526720589917</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.7951074725178753</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.6652029738561058</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.7152171289012541</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.1264205488937904</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.8316452677716271</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13.457577618329525</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13.566653715262163</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.546862396672884</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17.362200295623204</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.80054707614276</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.329591279007278</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.762628410378095</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20.467853129255932</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2DB8-44F9-87F9-572A3EA16B88}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1623713439"/>
+        <c:axId val="1623701919"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1623713439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1623701919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1623701919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-AR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1623713439"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-AR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1229,6 +2223,47 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>523876</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F4327CE-3031-2E19-DF7B-934F6B28D698}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -1561,7 +2596,7 @@
         <v>640</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1580,7 +2615,7 @@
         <v>102</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1591,7 +2626,7 @@
         <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1626,7 +2661,7 @@
         <v>202</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1960,7 +2995,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2502,16 +3537,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -2809,35 +3844,65 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>36.4</v>
       </c>
       <c r="B2" s="1">
         <v>3.8</v>
       </c>
-      <c r="C2" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C2" s="2">
+        <f>1/A2</f>
+        <v>2.7472527472527472E-2</v>
+      </c>
+      <c r="D2">
+        <f>C2*1000</f>
+        <v>27.472527472527471</v>
+      </c>
+      <c r="E2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="F2">
+        <f>2*PI()*E2</f>
+        <v>23.876104167282428</v>
+      </c>
+      <c r="G2">
+        <f>F2/D2</f>
+        <v>0.86909019168908042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>36.6</v>
       </c>
@@ -2845,42 +3910,134 @@
         <v>6.8</v>
       </c>
       <c r="C3" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <f t="shared" ref="C3:C11" si="0">1/A3</f>
+        <v>2.7322404371584699E-2</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D21" si="1">C3*1000</f>
+        <v>27.3224043715847</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F21" si="2">2*PI()*E3</f>
+        <v>42.725660088821186</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G21" si="3">F3/D3</f>
+        <v>1.5637591592508555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>36.799999999999997</v>
       </c>
       <c r="B4" s="1">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7173913043478264E-2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>27.173913043478265</v>
+      </c>
+      <c r="E4" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="2"/>
+        <v>61.575216010359952</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="3"/>
+        <v>2.2659679491812459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>37</v>
       </c>
       <c r="B5" s="1">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>27.027027027027028</v>
+      </c>
+      <c r="E5" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>80.424771931898704</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="3"/>
+        <v>2.9757165614802519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>37.200000000000003</v>
       </c>
       <c r="B6" s="1">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6881720430107524E-2</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>26.881720430107524</v>
+      </c>
+      <c r="E6" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="2"/>
+        <v>98.017690792001545</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="3"/>
+        <v>3.6462580974624577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>37.4</v>
       </c>
       <c r="B7" s="1">
         <v>18.399999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6737967914438502E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>26.737967914438503</v>
+      </c>
+      <c r="E7" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>115.61060965210437</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="3"/>
+        <v>4.3238368009887038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>37.6</v>
       </c>
@@ -2888,159 +4045,887 @@
         <v>21.2</v>
       </c>
       <c r="C8" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>2.6595744680851064E-2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>26.595744680851062</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>133.20352851220721</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="3"/>
+        <v>5.0084526720589917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>37.799999999999997</v>
       </c>
       <c r="B9" s="1">
         <v>24.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6455026455026457E-2</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>26.455026455026456</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>153.30972149518189</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="3"/>
+        <v>5.7951074725178753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>38</v>
       </c>
       <c r="B10" s="1">
         <v>1.6</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>26.315789473684209</v>
+      </c>
+      <c r="E10">
+        <f>B10+D10</f>
+        <v>27.91578947368421</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>175.40007825937118</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="3"/>
+        <v>6.6652029738561058</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>38.200000000000003</v>
       </c>
       <c r="B11" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>2.6178010471204185E-2</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>26.178010471204185</v>
+      </c>
+      <c r="E11">
+        <f>B11+D11</f>
+        <v>27.978010471204186</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>175.79102431678675</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>6.7152171289012541</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>38.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>38.6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="C12" s="1">
+        <f>1/A12</f>
+        <v>2.5906735751295335E-2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>25.906735751295336</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:E13" si="4">B12+D12</f>
+        <v>33.506735751295338</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>210.52902976408782</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>8.1264205488937904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1">
+        <v>10.4</v>
+      </c>
+      <c r="C13">
+        <f>1/A13</f>
+        <v>2.564102564102564E-2</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>25.641025641025639</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="4"/>
+        <v>36.041025641025641</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>226.45244276337505</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>8.8316452677716271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>39.4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="C14">
+        <f>1/A14</f>
+        <v>2.5380710659898477E-2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>25.380710659898476</v>
+      </c>
+      <c r="E14">
+        <f>B14+D14*2</f>
+        <v>54.361421319796953</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>341.56288371394731</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>13.457577618329525</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <f t="shared" ref="C15:C21" si="5">1/A15</f>
+        <v>2.5125628140703519E-2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>25.125628140703519</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ref="E15:E21" si="6">B15+D15*2</f>
+        <v>54.251256281407038</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>340.87069636337094</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>13.566653715262163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="B16" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="5"/>
+        <v>2.4875621890547261E-2</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>24.875621890547261</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="6"/>
+        <v>61.551243781094527</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>386.73787056400204</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>15.546862396672884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>40.6</v>
+      </c>
+      <c r="B17" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="5"/>
+        <v>2.463054187192118E-2</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>24.630541871921181</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="6"/>
+        <v>68.06108374384236</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="2"/>
+        <v>427.64040137002968</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>17.362200295623204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="5"/>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>24.390243902439025</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="6"/>
+        <v>72.980487804878052</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>458.54992868640875</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="3"/>
+        <v>18.80054707614276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="5"/>
+        <v>2.4154589371980676E-2</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>24.154589371980677</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="6"/>
+        <v>74.309178743961354</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>466.8983400726396</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>19.329591279007278</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="B20" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="5"/>
+        <v>2.3923444976076555E-2</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>23.923444976076556</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="6"/>
+        <v>75.246889952153111</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>472.79015335832764</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>19.762628410378095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>42.2</v>
+      </c>
+      <c r="B21" s="1">
+        <v>29.8</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="5"/>
+        <v>2.3696682464454975E-2</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>23.696682464454973</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="6"/>
+        <v>77.193364928909944</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>485.02021633307891</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>20.467853129255932</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87AE86C0-7473-4101-A390-48B305466A60}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>36.4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2.7472527472527472E-2</v>
+      </c>
+      <c r="D2">
+        <v>27.472527472527471</v>
+      </c>
+      <c r="E2">
+        <v>3.8</v>
+      </c>
+      <c r="F2">
+        <v>23.876104167282428</v>
+      </c>
+      <c r="G2">
+        <v>0.86909019168908042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>36.6</v>
+      </c>
+      <c r="B3" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.7322404371584699E-2</v>
+      </c>
+      <c r="D3">
+        <v>27.3224043715847</v>
+      </c>
+      <c r="E3">
+        <v>6.8</v>
+      </c>
+      <c r="F3">
+        <v>42.725660088821186</v>
+      </c>
+      <c r="G3">
+        <v>1.5637591592508555</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.7173913043478264E-2</v>
+      </c>
+      <c r="D4">
+        <v>27.173913043478265</v>
+      </c>
+      <c r="E4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="F4">
+        <v>61.575216010359952</v>
+      </c>
+      <c r="G4">
+        <v>2.2659679491812459</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.7027027027027029E-2</v>
+      </c>
+      <c r="D5">
+        <v>27.027027027027028</v>
+      </c>
+      <c r="E5">
+        <v>12.8</v>
+      </c>
+      <c r="F5">
+        <v>80.424771931898704</v>
+      </c>
+      <c r="G5">
+        <v>2.9757165614802519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="B6" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.6881720430107524E-2</v>
+      </c>
+      <c r="D6">
+        <v>26.881720430107524</v>
+      </c>
+      <c r="E6">
+        <v>15.6</v>
+      </c>
+      <c r="F6">
+        <v>98.017690792001545</v>
+      </c>
+      <c r="G6">
+        <v>3.6462580974624577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>37.4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.6737967914438502E-2</v>
+      </c>
+      <c r="D7">
+        <v>26.737967914438503</v>
+      </c>
+      <c r="E7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F7">
+        <v>115.61060965210437</v>
+      </c>
+      <c r="G7">
+        <v>4.3238368009887038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>37.6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.6595744680851064E-2</v>
+      </c>
+      <c r="D8">
+        <v>26.595744680851062</v>
+      </c>
+      <c r="E8">
+        <v>21.2</v>
+      </c>
+      <c r="F8">
+        <v>133.20352851220721</v>
+      </c>
+      <c r="G8">
+        <v>5.0084526720589917</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="B9" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.6455026455026457E-2</v>
+      </c>
+      <c r="D9">
+        <v>26.455026455026456</v>
+      </c>
+      <c r="E9">
+        <v>24.4</v>
+      </c>
+      <c r="F9">
+        <v>153.30972149518189</v>
+      </c>
+      <c r="G9">
+        <v>5.7951074725178753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="D10">
+        <v>26.315789473684209</v>
+      </c>
+      <c r="E10">
+        <v>27.91578947368421</v>
+      </c>
+      <c r="F10">
+        <v>175.40007825937118</v>
+      </c>
+      <c r="G10">
+        <v>6.6652029738561058</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.6178010471204185E-2</v>
+      </c>
+      <c r="D11">
+        <v>26.178010471204185</v>
+      </c>
+      <c r="E11">
+        <v>27.978010471204186</v>
+      </c>
+      <c r="F11">
+        <v>175.79102431678675</v>
+      </c>
+      <c r="G11">
+        <v>6.7152171289012541</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>38.6</v>
       </c>
+      <c r="B12" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.5906735751295335E-2</v>
+      </c>
+      <c r="D12">
+        <v>25.906735751295336</v>
+      </c>
+      <c r="E12">
+        <v>33.506735751295338</v>
+      </c>
+      <c r="F12">
+        <v>210.52902976408782</v>
+      </c>
+      <c r="G12">
+        <v>8.1264205488937904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>39</v>
+      </c>
       <c r="B13" s="1">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>10.4</v>
+      </c>
+      <c r="C13">
+        <v>2.564102564102564E-2</v>
+      </c>
+      <c r="D13">
+        <v>25.641025641025639</v>
+      </c>
+      <c r="E13">
+        <v>36.041025641025641</v>
+      </c>
+      <c r="F13">
+        <v>226.45244276337505</v>
+      </c>
+      <c r="G13">
+        <v>8.8316452677716271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>38.799999999999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>39.4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="C14">
+        <v>2.5380710659898477E-2</v>
+      </c>
+      <c r="D14">
+        <v>25.380710659898476</v>
+      </c>
+      <c r="E14">
+        <v>54.361421319796953</v>
+      </c>
+      <c r="F14">
+        <v>341.56288371394731</v>
+      </c>
+      <c r="G14">
+        <v>13.457577618329525</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>39</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="B15" s="1">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>2.5125628140703519E-2</v>
+      </c>
+      <c r="D15">
+        <v>25.125628140703519</v>
+      </c>
+      <c r="E15">
+        <v>54.251256281407038</v>
+      </c>
+      <c r="F15">
+        <v>340.87069636337094</v>
+      </c>
+      <c r="G15">
+        <v>13.566653715262163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>39.200000000000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="B16" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="C16">
+        <v>2.4875621890547261E-2</v>
+      </c>
+      <c r="D16">
+        <v>24.875621890547261</v>
+      </c>
+      <c r="E16">
+        <v>61.551243781094527</v>
+      </c>
+      <c r="F16">
+        <v>386.73787056400204</v>
+      </c>
+      <c r="G16">
+        <v>15.546862396672884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>39.4</v>
+        <v>40.6</v>
       </c>
       <c r="B17" s="1">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>18.8</v>
+      </c>
+      <c r="C17">
+        <v>2.463054187192118E-2</v>
+      </c>
+      <c r="D17">
+        <v>24.630541871921181</v>
+      </c>
+      <c r="E17">
+        <v>68.06108374384236</v>
+      </c>
+      <c r="F17">
+        <v>427.64040137002968</v>
+      </c>
+      <c r="G17">
+        <v>17.362200295623204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>39.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="B18" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="C18">
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="D18">
+        <v>24.390243902439025</v>
+      </c>
+      <c r="E18">
+        <v>72.980487804878052</v>
+      </c>
+      <c r="F18">
+        <v>458.54992868640875</v>
+      </c>
+      <c r="G18">
+        <v>18.80054707614276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>39.799999999999997</v>
+        <v>41.4</v>
       </c>
       <c r="B19" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>2.4154589371980676E-2</v>
+      </c>
+      <c r="D19">
+        <v>24.154589371980677</v>
+      </c>
+      <c r="E19">
+        <v>74.309178743961354</v>
+      </c>
+      <c r="F19">
+        <v>466.8983400726396</v>
+      </c>
+      <c r="G19">
+        <v>19.329591279007278</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>41.8</v>
+      </c>
+      <c r="B20" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="C20">
+        <v>2.3923444976076555E-2</v>
+      </c>
+      <c r="D20">
+        <v>23.923444976076556</v>
+      </c>
+      <c r="E20">
+        <v>75.246889952153111</v>
+      </c>
+      <c r="F20">
+        <v>472.79015335832764</v>
+      </c>
+      <c r="G20">
+        <v>19.762628410378095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>40.200000000000003</v>
+        <v>42.2</v>
       </c>
       <c r="B21" s="1">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>40.6</v>
-      </c>
-      <c r="B23" s="1">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>40.799999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>41</v>
-      </c>
-      <c r="B25" s="1">
-        <v>24.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>41.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>41.4</v>
-      </c>
-      <c r="B27" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>41.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>41.8</v>
-      </c>
-      <c r="B29" s="1">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>42.2</v>
-      </c>
-      <c r="B30" s="1">
         <v>29.8</v>
+      </c>
+      <c r="C21">
+        <v>2.3696682464454975E-2</v>
+      </c>
+      <c r="D21">
+        <v>23.696682464454973</v>
+      </c>
+      <c r="E21">
+        <v>77.193364928909944</v>
+      </c>
+      <c r="F21">
+        <v>485.02021633307891</v>
+      </c>
+      <c r="G21">
+        <v>20.467853129255932</v>
       </c>
     </row>
   </sheetData>
@@ -3048,7 +4933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3058,19 +4943,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G1" s="1">
         <v>39.46</v>
